--- a/performance_tracking_forms/023_driver_performance_quarterly_report_form--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/023_driver_performance_quarterly_report_form--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,115 +515,119 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_1</t>
+          <t>overall_performance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_1_label</t>
+          <t>Overall Performance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_2</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>performance_quarterly_feedback</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide feedback on the driver's performance</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_3</t>
+          <t>performance_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fleet_performance_quarterly_tracking</t>
+          <t>Performance Frequency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_4</t>
+          <t>performance_duration</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>consistent_performance_feedback</t>
+          <t>Performance Duration</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>performance_quarterly_rating</t>
+          <t>fleet_performance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>performance_quarterly_rating</t>
+          <t>Fleet Performance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +639,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_6</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fleet_performance_quarterly_rating</t>
+          <t>Overall Rating</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +662,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_7</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>overall_performance_quarterly_rating</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,64 +685,64 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>performance_quarterly_comments</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>performance_quarterly_comments</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_9</t>
+          <t>performance_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_9_label</t>
+          <t>Performance Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_10</t>
+          <t>good_performance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>performance_quarterly_frequency</t>
+          <t>Good Performance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,64 +754,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_11</t>
+          <t>good_duration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>performance_quarterly_duration</t>
+          <t>Good Duration</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_12</t>
+          <t>overall_rating_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>performance_quarterly_frequency</t>
+          <t>Overall Rating 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_13</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_13_label</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,64 +823,64 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>performance_quarterly_rating</t>
+          <t>fleet_rating</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>performance_quarterly_rating</t>
+          <t>Fleet Rating</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_15</t>
+          <t>fleet_comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_15_label</t>
+          <t>Fleet Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_16</t>
+          <t>overall_performance_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>performance_quarterly_frequency</t>
+          <t>Overall Performance 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,41 +892,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_17</t>
+          <t>performance_frequency_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>performance_quarterly_duration</t>
+          <t>Performance Frequency 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_18</t>
+          <t>overall_rating_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_18_label</t>
+          <t>Overall Rating 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -937,12 +941,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -965,255 +969,204 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_2_choices</t>
+          <t>overall_performance_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_2_choices</t>
+          <t>overall_performance_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_2_choices</t>
+          <t>overall_performance_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement',_'value':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Needs Improvement', 'value': 'needs_improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_9_choices</t>
+          <t>fleet_performance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_9_choices</t>
+          <t>fleet_performance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_9_choices</t>
+          <t>fleet_performance_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement',_'value':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Needs Improvement', 'value': 'needs_improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_13_choices</t>
+          <t>good_performance_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_13_choices</t>
+          <t>good_performance_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_13_choices</t>
+          <t>good_performance_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement',_'value':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Needs Improvement', 'value': 'needs_improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_15_choices</t>
+          <t>overall_performance_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Excellent', 'value': 'excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_15_choices</t>
+          <t>overall_performance_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>driver_performance_quarterly_report_form_page_15_choices</t>
+          <t>overall_performance_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'needs_improvement',_'value':_'needs_improvement'}</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Needs Improvement', 'value': 'needs_improvement'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>driver_performance_quarterly_report_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'label':_'excellent',_'value':_'excellent'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'label': 'Excellent', 'value': 'excellent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>driver_performance_quarterly_report_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>driver_performance_quarterly_report_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'label':_'needs_improvement',_'value':_'needs_improvement'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'label': 'Needs Improvement', 'value': 'needs_improvement'}</t>
+          <t>Needs Improvement</t>
         </is>
       </c>
     </row>
